--- a/data/Data_UpdateCart.xlsx
+++ b/data/Data_UpdateCart.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\project_demo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7BC97D6-1BF8-4A90-860A-54EBA29AA98F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C339C82-05E3-4C84-94E8-D192CD49B0FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9C6C6A52-4974-435E-A64B-CE6E2E68C084}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>username</t>
   </si>
@@ -76,9 +76,6 @@
   </si>
   <si>
     <t>phindi kem sữa</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
 </sst>
 </file>
@@ -449,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1477CE-308C-43F9-A367-E1A5A631C367}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.109375" customWidth="1"/>
@@ -575,11 +572,6 @@
         <v>100000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E12" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
